--- a/results/standard/UNEP-EGR-2026-total-sector-trend.xlsx
+++ b/results/standard/UNEP-EGR-2026-total-sector-trend.xlsx
@@ -472,7 +472,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>7.68013294786169</v>
+        <v>7.67925343879397</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -486,7 +486,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>3.97966712939437</v>
+        <v>3.96957916050504</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -500,7 +500,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>4.70765047851209</v>
+        <v>4.70700085725202</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -514,7 +514,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>3.70008417790288</v>
+        <v>3.71628481578111</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -528,7 +528,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>3.73132242992434</v>
+        <v>3.73713074482721</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -542,7 +542,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>1.92775627397292</v>
+        <v>1.88191340447504</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -556,7 +556,7 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>4.98390892041311</v>
+        <v>4.98994953530623</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -584,7 +584,7 @@
         <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>1.46517258843825</v>
+        <v>1.38006416710242</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -598,7 +598,7 @@
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>7.83037922667294</v>
+        <v>7.82949573365587</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -612,7 +612,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>3.90123388097743</v>
+        <v>3.89364057741328</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -626,7 +626,7 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>4.74704133223151</v>
+        <v>4.74629055120307</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -640,7 +640,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>3.72718060247837</v>
+        <v>3.74372483280972</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
@@ -654,7 +654,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>3.65601579679921</v>
+        <v>3.66203194931321</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -668,7 +668,7 @@
         <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>1.92664923352497</v>
+        <v>1.85896341833713</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
@@ -682,7 +682,7 @@
         <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>4.95782545799573</v>
+        <v>4.95686707293805</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -710,7 +710,7 @@
         <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>1.50868829102196</v>
+        <v>1.42987137296595</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
@@ -724,7 +724,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>7.96761282571007</v>
+        <v>7.9666636369845</v>
       </c>
       <c r="D20" t="s">
         <v>13</v>
@@ -738,7 +738,7 @@
         <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>3.77203315063058</v>
+        <v>3.76188621395884</v>
       </c>
       <c r="D21" t="s">
         <v>13</v>
@@ -752,7 +752,7 @@
         <v>15</v>
       </c>
       <c r="C22" t="n">
-        <v>4.85588646443966</v>
+        <v>4.85507211008334</v>
       </c>
       <c r="D22" t="s">
         <v>13</v>
@@ -766,7 +766,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>3.53074456333502</v>
+        <v>3.54716126990027</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
@@ -780,7 +780,7 @@
         <v>17</v>
       </c>
       <c r="C24" t="n">
-        <v>3.67201181056933</v>
+        <v>3.67870121481529</v>
       </c>
       <c r="D24" t="s">
         <v>13</v>
@@ -794,7 +794,7 @@
         <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>1.95213560637676</v>
+        <v>1.87366524590038</v>
       </c>
       <c r="D25" t="s">
         <v>13</v>
@@ -808,7 +808,7 @@
         <v>19</v>
       </c>
       <c r="C26" t="n">
-        <v>4.96275527629892</v>
+        <v>4.96382742945809</v>
       </c>
       <c r="D26" t="s">
         <v>13</v>
@@ -836,7 +836,7 @@
         <v>21</v>
       </c>
       <c r="C28" t="n">
-        <v>1.50354461250096</v>
+        <v>1.43108437594405</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
@@ -850,7 +850,7 @@
         <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>7.99000917915321</v>
+        <v>7.9890937296107</v>
       </c>
       <c r="D29" t="s">
         <v>13</v>
@@ -864,7 +864,7 @@
         <v>14</v>
       </c>
       <c r="C30" t="n">
-        <v>3.72038063174533</v>
+        <v>3.70818072350298</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
       <c r="C31" t="n">
-        <v>4.89788606169097</v>
+        <v>4.89717475619422</v>
       </c>
       <c r="D31" t="s">
         <v>13</v>
@@ -892,7 +892,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>3.60647722375168</v>
+        <v>3.62339430725617</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
@@ -906,7 +906,7 @@
         <v>17</v>
       </c>
       <c r="C33" t="n">
-        <v>3.65670475270099</v>
+        <v>3.6635522357463</v>
       </c>
       <c r="D33" t="s">
         <v>13</v>
@@ -920,7 +920,7 @@
         <v>18</v>
       </c>
       <c r="C34" t="n">
-        <v>1.98237026847984</v>
+        <v>1.88741134303038</v>
       </c>
       <c r="D34" t="s">
         <v>13</v>
@@ -934,7 +934,7 @@
         <v>19</v>
       </c>
       <c r="C35" t="n">
-        <v>4.92707037675531</v>
+        <v>4.9248227465612</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
@@ -962,7 +962,7 @@
         <v>21</v>
       </c>
       <c r="C37" t="n">
-        <v>1.51745380717617</v>
+        <v>1.45231651937553</v>
       </c>
       <c r="D37" t="s">
         <v>13</v>
@@ -976,7 +976,7 @@
         <v>12</v>
       </c>
       <c r="C38" t="n">
-        <v>8.07277298636896</v>
+        <v>8.07173327777046</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
@@ -990,7 +990,7 @@
         <v>14</v>
       </c>
       <c r="C39" t="n">
-        <v>3.7339625641872</v>
+        <v>3.72381876697122</v>
       </c>
       <c r="D39" t="s">
         <v>13</v>
@@ -1004,7 +1004,7 @@
         <v>15</v>
       </c>
       <c r="C40" t="n">
-        <v>4.9986984328297</v>
+        <v>4.99772618067352</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
@@ -1018,7 +1018,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>3.49002275047065</v>
+        <v>3.50721695055239</v>
       </c>
       <c r="D41" t="s">
         <v>13</v>
@@ -1032,7 +1032,7 @@
         <v>17</v>
       </c>
       <c r="C42" t="n">
-        <v>3.78701177854742</v>
+        <v>3.79371472036787</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
@@ -1046,7 +1046,7 @@
         <v>18</v>
       </c>
       <c r="C43" t="n">
-        <v>2.07756052936171</v>
+        <v>1.96373694631369</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
@@ -1060,7 +1060,7 @@
         <v>19</v>
       </c>
       <c r="C44" t="n">
-        <v>4.97086385917547</v>
+        <v>4.9696594984114</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
@@ -1088,7 +1088,7 @@
         <v>21</v>
       </c>
       <c r="C46" t="n">
-        <v>1.52725157411883</v>
+        <v>1.46954143396105</v>
       </c>
       <c r="D46" t="s">
         <v>13</v>
@@ -1102,7 +1102,7 @@
         <v>12</v>
       </c>
       <c r="C47" t="n">
-        <v>8.23242143343871</v>
+        <v>8.23137897668217</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
@@ -1116,7 +1116,7 @@
         <v>14</v>
       </c>
       <c r="C48" t="n">
-        <v>3.95793205368093</v>
+        <v>3.94697025927457</v>
       </c>
       <c r="D48" t="s">
         <v>13</v>
@@ -1130,7 +1130,7 @@
         <v>15</v>
       </c>
       <c r="C49" t="n">
-        <v>5.13716899486601</v>
+        <v>5.13620546411857</v>
       </c>
       <c r="D49" t="s">
         <v>13</v>
@@ -1144,7 +1144,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>3.5197817158213</v>
+        <v>3.53797539970376</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>
@@ -1158,7 +1158,7 @@
         <v>17</v>
       </c>
       <c r="C51" t="n">
-        <v>3.87651625338291</v>
+        <v>3.8827329283588</v>
       </c>
       <c r="D51" t="s">
         <v>13</v>
@@ -1172,7 +1172,7 @@
         <v>18</v>
       </c>
       <c r="C52" t="n">
-        <v>2.19641633408145</v>
+        <v>2.07236529637586</v>
       </c>
       <c r="D52" t="s">
         <v>13</v>
@@ -1186,7 +1186,7 @@
         <v>19</v>
       </c>
       <c r="C53" t="n">
-        <v>5.02428182286735</v>
+        <v>5.02400416742048</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
@@ -1214,7 +1214,7 @@
         <v>21</v>
       </c>
       <c r="C55" t="n">
-        <v>1.54261945752165</v>
+        <v>1.49361086982945</v>
       </c>
       <c r="D55" t="s">
         <v>13</v>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="C56" t="n">
-        <v>8.57881371367793</v>
+        <v>8.57780069213201</v>
       </c>
       <c r="D56" t="s">
         <v>13</v>
@@ -1242,7 +1242,7 @@
         <v>14</v>
       </c>
       <c r="C57" t="n">
-        <v>3.84029779445789</v>
+        <v>3.82956167063333</v>
       </c>
       <c r="D57" t="s">
         <v>13</v>
@@ -1256,7 +1256,7 @@
         <v>15</v>
       </c>
       <c r="C58" t="n">
-        <v>5.34897527649882</v>
+        <v>5.34799422163667</v>
       </c>
       <c r="D58" t="s">
         <v>13</v>
@@ -1270,7 +1270,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>3.50491839916845</v>
+        <v>3.52469354592003</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
@@ -1284,7 +1284,7 @@
         <v>17</v>
       </c>
       <c r="C60" t="n">
-        <v>3.97696375521624</v>
+        <v>3.98253965484962</v>
       </c>
       <c r="D60" t="s">
         <v>13</v>
@@ -1298,7 +1298,7 @@
         <v>18</v>
       </c>
       <c r="C61" t="n">
-        <v>2.25476434134673</v>
+        <v>2.1251111859471</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
@@ -1312,7 +1312,7 @@
         <v>19</v>
       </c>
       <c r="C62" t="n">
-        <v>5.06695929765529</v>
+        <v>5.06648107661924</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
@@ -1340,7 +1340,7 @@
         <v>21</v>
       </c>
       <c r="C64" t="n">
-        <v>1.55192820647332</v>
+        <v>1.50984208047864</v>
       </c>
       <c r="D64" t="s">
         <v>13</v>
@@ -1354,7 +1354,7 @@
         <v>12</v>
       </c>
       <c r="C65" t="n">
-        <v>8.80123273412106</v>
+        <v>8.80008150101474</v>
       </c>
       <c r="D65" t="s">
         <v>13</v>
@@ -1368,7 +1368,7 @@
         <v>14</v>
       </c>
       <c r="C66" t="n">
-        <v>3.86448245084977</v>
+        <v>3.85429875875352</v>
       </c>
       <c r="D66" t="s">
         <v>13</v>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
       <c r="C67" t="n">
-        <v>5.43025901935264</v>
+        <v>5.4292127465065</v>
       </c>
       <c r="D67" t="s">
         <v>13</v>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>3.53723174097013</v>
+        <v>3.55788608614735</v>
       </c>
       <c r="D68" t="s">
         <v>13</v>
@@ -1410,7 +1410,7 @@
         <v>17</v>
       </c>
       <c r="C69" t="n">
-        <v>4.04540083763661</v>
+        <v>4.05106700213164</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -1424,7 +1424,7 @@
         <v>18</v>
       </c>
       <c r="C70" t="n">
-        <v>2.31661486690367</v>
+        <v>2.18027124651531</v>
       </c>
       <c r="D70" t="s">
         <v>13</v>
@@ -1438,7 +1438,7 @@
         <v>19</v>
       </c>
       <c r="C71" t="n">
-        <v>4.99680317395394</v>
+        <v>4.99595047983896</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
@@ -1466,7 +1466,7 @@
         <v>21</v>
       </c>
       <c r="C73" t="n">
-        <v>1.53869008111307</v>
+        <v>1.50515360604645</v>
       </c>
       <c r="D73" t="s">
         <v>13</v>
@@ -1480,7 +1480,7 @@
         <v>12</v>
       </c>
       <c r="C74" t="n">
-        <v>8.98691019712217</v>
+        <v>8.986170597358</v>
       </c>
       <c r="D74" t="s">
         <v>13</v>
@@ -1494,7 +1494,7 @@
         <v>14</v>
       </c>
       <c r="C75" t="n">
-        <v>3.86259217310473</v>
+        <v>3.85211772105998</v>
       </c>
       <c r="D75" t="s">
         <v>13</v>
@@ -1508,7 +1508,7 @@
         <v>15</v>
       </c>
       <c r="C76" t="n">
-        <v>5.56083041765307</v>
+        <v>5.55976784715663</v>
       </c>
       <c r="D76" t="s">
         <v>13</v>
@@ -1522,7 +1522,7 @@
         <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>3.35713827160989</v>
+        <v>3.37671183933596</v>
       </c>
       <c r="D77" t="s">
         <v>13</v>
@@ -1536,7 +1536,7 @@
         <v>17</v>
       </c>
       <c r="C78" t="n">
-        <v>3.98042245661781</v>
+        <v>3.98554582655749</v>
       </c>
       <c r="D78" t="s">
         <v>13</v>
@@ -1550,7 +1550,7 @@
         <v>18</v>
       </c>
       <c r="C79" t="n">
-        <v>2.32793692786911</v>
+        <v>2.19348430546866</v>
       </c>
       <c r="D79" t="s">
         <v>13</v>
@@ -1564,7 +1564,7 @@
         <v>19</v>
       </c>
       <c r="C80" t="n">
-        <v>5.01556504565106</v>
+        <v>5.01297823565737</v>
       </c>
       <c r="D80" t="s">
         <v>13</v>
@@ -1592,7 +1592,7 @@
         <v>21</v>
       </c>
       <c r="C82" t="n">
-        <v>1.55630825976992</v>
+        <v>1.52861808458887</v>
       </c>
       <c r="D82" t="s">
         <v>13</v>
@@ -1606,7 +1606,7 @@
         <v>12</v>
       </c>
       <c r="C83" t="n">
-        <v>9.06620202910009</v>
+        <v>9.06613513014723</v>
       </c>
       <c r="D83" t="s">
         <v>13</v>
@@ -1620,7 +1620,7 @@
         <v>14</v>
       </c>
       <c r="C84" t="n">
-        <v>3.705415310078</v>
+        <v>3.69684781656607</v>
       </c>
       <c r="D84" t="s">
         <v>13</v>
@@ -1634,7 +1634,7 @@
         <v>15</v>
       </c>
       <c r="C85" t="n">
-        <v>5.72988281793433</v>
+        <v>5.72897978649713</v>
       </c>
       <c r="D85" t="s">
         <v>13</v>
@@ -1648,7 +1648,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>3.43796496511603</v>
+        <v>3.45672960038701</v>
       </c>
       <c r="D86" t="s">
         <v>13</v>
@@ -1662,7 +1662,7 @@
         <v>17</v>
       </c>
       <c r="C87" t="n">
-        <v>3.93868580057933</v>
+        <v>3.94248076256764</v>
       </c>
       <c r="D87" t="s">
         <v>13</v>
@@ -1676,7 +1676,7 @@
         <v>18</v>
       </c>
       <c r="C88" t="n">
-        <v>2.37293213660096</v>
+        <v>2.23198761061892</v>
       </c>
       <c r="D88" t="s">
         <v>13</v>
@@ -1690,7 +1690,7 @@
         <v>19</v>
       </c>
       <c r="C89" t="n">
-        <v>5.07319171645875</v>
+        <v>5.07273123011763</v>
       </c>
       <c r="D89" t="s">
         <v>13</v>
@@ -1718,7 +1718,7 @@
         <v>21</v>
       </c>
       <c r="C91" t="n">
-        <v>1.55987900310047</v>
+        <v>1.54366852131026</v>
       </c>
       <c r="D91" t="s">
         <v>13</v>
@@ -1732,7 +1732,7 @@
         <v>12</v>
       </c>
       <c r="C92" t="n">
-        <v>9.44851337282472</v>
+        <v>9.44240968869954</v>
       </c>
       <c r="D92" t="s">
         <v>13</v>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
       <c r="C93" t="n">
-        <v>3.86122748663037</v>
+        <v>3.84968348154793</v>
       </c>
       <c r="D93" t="s">
         <v>13</v>
@@ -1760,7 +1760,7 @@
         <v>15</v>
       </c>
       <c r="C94" t="n">
-        <v>5.89123740207719</v>
+        <v>5.89000705514814</v>
       </c>
       <c r="D94" t="s">
         <v>13</v>
@@ -1774,7 +1774,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>3.36327775627442</v>
+        <v>3.38230158580149</v>
       </c>
       <c r="D95" t="s">
         <v>13</v>
@@ -1788,7 +1788,7 @@
         <v>17</v>
       </c>
       <c r="C96" t="n">
-        <v>4.07880634749852</v>
+        <v>4.08389038117359</v>
       </c>
       <c r="D96" t="s">
         <v>13</v>
@@ -1802,7 +1802,7 @@
         <v>18</v>
       </c>
       <c r="C97" t="n">
-        <v>2.46866756569866</v>
+        <v>2.306337472367</v>
       </c>
       <c r="D97" t="s">
         <v>13</v>
@@ -1816,7 +1816,7 @@
         <v>19</v>
       </c>
       <c r="C98" t="n">
-        <v>5.06401035612561</v>
+        <v>5.06353578533946</v>
       </c>
       <c r="D98" t="s">
         <v>13</v>
@@ -1844,7 +1844,7 @@
         <v>21</v>
       </c>
       <c r="C100" t="n">
-        <v>1.57821735993014</v>
+        <v>1.57079540270491</v>
       </c>
       <c r="D100" t="s">
         <v>13</v>
@@ -1858,7 +1858,7 @@
         <v>12</v>
       </c>
       <c r="C101" t="n">
-        <v>9.65465239490288</v>
+        <v>9.65460786928782</v>
       </c>
       <c r="D101" t="s">
         <v>13</v>
@@ -1872,7 +1872,7 @@
         <v>14</v>
       </c>
       <c r="C102" t="n">
-        <v>3.88324844937531</v>
+        <v>3.86846051173296</v>
       </c>
       <c r="D102" t="s">
         <v>13</v>
@@ -1886,7 +1886,7 @@
         <v>15</v>
       </c>
       <c r="C103" t="n">
-        <v>5.92107768581903</v>
+        <v>5.91984201449464</v>
       </c>
       <c r="D103" t="s">
         <v>13</v>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>3.3954038140001</v>
+        <v>3.41676260641119</v>
       </c>
       <c r="D104" t="s">
         <v>13</v>
@@ -1914,7 +1914,7 @@
         <v>17</v>
       </c>
       <c r="C105" t="n">
-        <v>4.06273462576126</v>
+        <v>4.06773219874705</v>
       </c>
       <c r="D105" t="s">
         <v>13</v>
@@ -1928,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="C106" t="n">
-        <v>2.48946293852612</v>
+        <v>2.32779334942594</v>
       </c>
       <c r="D106" t="s">
         <v>13</v>
@@ -1942,7 +1942,7 @@
         <v>19</v>
       </c>
       <c r="C107" t="n">
-        <v>5.07198053166717</v>
+        <v>5.07015244590779</v>
       </c>
       <c r="D107" t="s">
         <v>13</v>
@@ -1970,7 +1970,7 @@
         <v>21</v>
       </c>
       <c r="C109" t="n">
-        <v>1.58244337628977</v>
+        <v>1.57912590498257</v>
       </c>
       <c r="D109" t="s">
         <v>13</v>
@@ -1984,7 +1984,7 @@
         <v>12</v>
       </c>
       <c r="C110" t="n">
-        <v>9.79299652954228</v>
+        <v>9.79279621183091</v>
       </c>
       <c r="D110" t="s">
         <v>13</v>
@@ -1998,7 +1998,7 @@
         <v>14</v>
       </c>
       <c r="C111" t="n">
-        <v>3.89463530088336</v>
+        <v>3.87488734892873</v>
       </c>
       <c r="D111" t="s">
         <v>13</v>
@@ -2012,7 +2012,7 @@
         <v>15</v>
       </c>
       <c r="C112" t="n">
-        <v>6.07613360137213</v>
+        <v>6.07489758575822</v>
       </c>
       <c r="D112" t="s">
         <v>13</v>
@@ -2026,7 +2026,7 @@
         <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>3.39636723795928</v>
+        <v>3.42055009113376</v>
       </c>
       <c r="D113" t="s">
         <v>13</v>
@@ -2040,7 +2040,7 @@
         <v>17</v>
       </c>
       <c r="C114" t="n">
-        <v>4.01795287476308</v>
+        <v>4.0222565368974</v>
       </c>
       <c r="D114" t="s">
         <v>13</v>
@@ -2054,7 +2054,7 @@
         <v>18</v>
       </c>
       <c r="C115" t="n">
-        <v>2.63162130264317</v>
+        <v>2.42020956524002</v>
       </c>
       <c r="D115" t="s">
         <v>13</v>
@@ -2068,7 +2068,7 @@
         <v>19</v>
       </c>
       <c r="C116" t="n">
-        <v>5.12641452379104</v>
+        <v>5.12470436368193</v>
       </c>
       <c r="D116" t="s">
         <v>13</v>
@@ -2096,7 +2096,7 @@
         <v>21</v>
       </c>
       <c r="C118" t="n">
-        <v>1.59316920957344</v>
+        <v>1.59666820467968</v>
       </c>
       <c r="D118" t="s">
         <v>13</v>
@@ -2110,7 +2110,7 @@
         <v>12</v>
       </c>
       <c r="C119" t="n">
-        <v>10.3534430580962</v>
+        <v>10.3534440440453</v>
       </c>
       <c r="D119" t="s">
         <v>13</v>
@@ -2124,7 +2124,7 @@
         <v>14</v>
       </c>
       <c r="C120" t="n">
-        <v>4.0872999212063</v>
+        <v>4.06580840949979</v>
       </c>
       <c r="D120" t="s">
         <v>13</v>
@@ -2138,7 +2138,7 @@
         <v>15</v>
       </c>
       <c r="C121" t="n">
-        <v>6.20440506545138</v>
+        <v>6.2031438660793</v>
       </c>
       <c r="D121" t="s">
         <v>13</v>
@@ -2152,7 +2152,7 @@
         <v>16</v>
       </c>
       <c r="C122" t="n">
-        <v>3.50563193318372</v>
+        <v>3.52892799689647</v>
       </c>
       <c r="D122" t="s">
         <v>13</v>
@@ -2166,7 +2166,7 @@
         <v>17</v>
       </c>
       <c r="C123" t="n">
-        <v>4.32547810761474</v>
+        <v>4.33111041901562</v>
       </c>
       <c r="D123" t="s">
         <v>13</v>
@@ -2180,7 +2180,7 @@
         <v>18</v>
       </c>
       <c r="C124" t="n">
-        <v>2.76183584025228</v>
+        <v>2.55831419944939</v>
       </c>
       <c r="D124" t="s">
         <v>13</v>
@@ -2194,7 +2194,7 @@
         <v>19</v>
       </c>
       <c r="C125" t="n">
-        <v>5.17970645169932</v>
+        <v>5.17742217234608</v>
       </c>
       <c r="D125" t="s">
         <v>13</v>
@@ -2222,7 +2222,7 @@
         <v>21</v>
       </c>
       <c r="C127" t="n">
-        <v>1.61442558516399</v>
+        <v>1.62182399647962</v>
       </c>
       <c r="D127" t="s">
         <v>13</v>
@@ -2236,7 +2236,7 @@
         <v>12</v>
       </c>
       <c r="C128" t="n">
-        <v>10.728137078409</v>
+        <v>10.7284049539886</v>
       </c>
       <c r="D128" t="s">
         <v>13</v>
@@ -2250,7 +2250,7 @@
         <v>14</v>
       </c>
       <c r="C129" t="n">
-        <v>4.51579619105139</v>
+        <v>4.49311289765176</v>
       </c>
       <c r="D129" t="s">
         <v>13</v>
@@ -2264,7 +2264,7 @@
         <v>15</v>
       </c>
       <c r="C130" t="n">
-        <v>6.49193606071219</v>
+        <v>6.49061366601665</v>
       </c>
       <c r="D130" t="s">
         <v>13</v>
@@ -2278,7 +2278,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>3.58675880791486</v>
+        <v>3.61142131523967</v>
       </c>
       <c r="D131" t="s">
         <v>13</v>
@@ -2292,7 +2292,7 @@
         <v>17</v>
       </c>
       <c r="C132" t="n">
-        <v>4.39386555954888</v>
+        <v>4.39965205431035</v>
       </c>
       <c r="D132" t="s">
         <v>13</v>
@@ -2306,7 +2306,7 @@
         <v>18</v>
       </c>
       <c r="C133" t="n">
-        <v>2.95493434172847</v>
+        <v>2.72533035453124</v>
       </c>
       <c r="D133" t="s">
         <v>13</v>
@@ -2320,7 +2320,7 @@
         <v>19</v>
       </c>
       <c r="C134" t="n">
-        <v>5.28975923509189</v>
+        <v>5.28606137436213</v>
       </c>
       <c r="D134" t="s">
         <v>13</v>
@@ -2348,7 +2348,7 @@
         <v>21</v>
       </c>
       <c r="C136" t="n">
-        <v>1.64140560187625</v>
+        <v>1.6428085188058</v>
       </c>
       <c r="D136" t="s">
         <v>13</v>
@@ -2362,7 +2362,7 @@
         <v>12</v>
       </c>
       <c r="C137" t="n">
-        <v>11.0765932134308</v>
+        <v>11.0763031763721</v>
       </c>
       <c r="D137" t="s">
         <v>13</v>
@@ -2376,7 +2376,7 @@
         <v>14</v>
       </c>
       <c r="C138" t="n">
-        <v>4.93715689279258</v>
+        <v>4.91014155120112</v>
       </c>
       <c r="D138" t="s">
         <v>13</v>
@@ -2390,7 +2390,7 @@
         <v>15</v>
       </c>
       <c r="C139" t="n">
-        <v>6.63355999188253</v>
+        <v>6.63229408955038</v>
       </c>
       <c r="D139" t="s">
         <v>13</v>
@@ -2404,7 +2404,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>3.61575225365727</v>
+        <v>3.64024652494412</v>
       </c>
       <c r="D140" t="s">
         <v>13</v>
@@ -2418,7 +2418,7 @@
         <v>17</v>
       </c>
       <c r="C141" t="n">
-        <v>4.5144369712572</v>
+        <v>4.52129449555942</v>
       </c>
       <c r="D141" t="s">
         <v>13</v>
@@ -2432,7 +2432,7 @@
         <v>18</v>
       </c>
       <c r="C142" t="n">
-        <v>3.13526445864175</v>
+        <v>2.91423845070088</v>
       </c>
       <c r="D142" t="s">
         <v>13</v>
@@ -2446,7 +2446,7 @@
         <v>19</v>
       </c>
       <c r="C143" t="n">
-        <v>5.3317108701973</v>
+        <v>5.32308147944771</v>
       </c>
       <c r="D143" t="s">
         <v>13</v>
@@ -2474,7 +2474,7 @@
         <v>21</v>
       </c>
       <c r="C145" t="n">
-        <v>1.65677737773444</v>
+        <v>1.6632767257646</v>
       </c>
       <c r="D145" t="s">
         <v>13</v>
@@ -2488,7 +2488,7 @@
         <v>12</v>
       </c>
       <c r="C146" t="n">
-        <v>11.5112897989126</v>
+        <v>11.5105546113803</v>
       </c>
       <c r="D146" t="s">
         <v>13</v>
@@ -2502,7 +2502,7 @@
         <v>14</v>
       </c>
       <c r="C147" t="n">
-        <v>5.17301273257268</v>
+        <v>5.14639692643837</v>
       </c>
       <c r="D147" t="s">
         <v>13</v>
@@ -2516,7 +2516,7 @@
         <v>15</v>
       </c>
       <c r="C148" t="n">
-        <v>6.78785485984847</v>
+        <v>6.78655846740081</v>
       </c>
       <c r="D148" t="s">
         <v>13</v>
@@ -2530,7 +2530,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>3.59495594523831</v>
+        <v>3.62131582508539</v>
       </c>
       <c r="D149" t="s">
         <v>13</v>
@@ -2544,7 +2544,7 @@
         <v>17</v>
       </c>
       <c r="C150" t="n">
-        <v>4.63358724950813</v>
+        <v>4.63939548626946</v>
       </c>
       <c r="D150" t="s">
         <v>13</v>
@@ -2558,7 +2558,7 @@
         <v>18</v>
       </c>
       <c r="C151" t="n">
-        <v>3.26060562577576</v>
+        <v>3.12196603723418</v>
       </c>
       <c r="D151" t="s">
         <v>13</v>
@@ -2572,7 +2572,7 @@
         <v>19</v>
       </c>
       <c r="C152" t="n">
-        <v>5.4107197294772</v>
+        <v>5.40244933324344</v>
       </c>
       <c r="D152" t="s">
         <v>13</v>
@@ -2600,7 +2600,7 @@
         <v>21</v>
       </c>
       <c r="C154" t="n">
-        <v>1.68477878252408</v>
+        <v>1.69841385415876</v>
       </c>
       <c r="D154" t="s">
         <v>13</v>
@@ -2614,7 +2614,7 @@
         <v>12</v>
       </c>
       <c r="C155" t="n">
-        <v>12.0144329453013</v>
+        <v>12.0140991540463</v>
       </c>
       <c r="D155" t="s">
         <v>13</v>
@@ -2628,7 +2628,7 @@
         <v>14</v>
       </c>
       <c r="C156" t="n">
-        <v>5.45351465356761</v>
+        <v>5.43169078707793</v>
       </c>
       <c r="D156" t="s">
         <v>13</v>
@@ -2642,7 +2642,7 @@
         <v>15</v>
       </c>
       <c r="C157" t="n">
-        <v>6.99898362152504</v>
+        <v>6.99813333863433</v>
       </c>
       <c r="D157" t="s">
         <v>13</v>
@@ -2656,7 +2656,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>3.5933677777063</v>
+        <v>3.61675727498007</v>
       </c>
       <c r="D158" t="s">
         <v>13</v>
@@ -2670,7 +2670,7 @@
         <v>17</v>
       </c>
       <c r="C159" t="n">
-        <v>4.64883063721019</v>
+        <v>4.65672561730883</v>
       </c>
       <c r="D159" t="s">
         <v>13</v>
@@ -2684,7 +2684,7 @@
         <v>18</v>
       </c>
       <c r="C160" t="n">
-        <v>3.42252335671739</v>
+        <v>3.28823023193237</v>
       </c>
       <c r="D160" t="s">
         <v>13</v>
@@ -2698,7 +2698,7 @@
         <v>19</v>
       </c>
       <c r="C161" t="n">
-        <v>5.47825646176729</v>
+        <v>5.46756427416482</v>
       </c>
       <c r="D161" t="s">
         <v>13</v>
@@ -2726,7 +2726,7 @@
         <v>21</v>
       </c>
       <c r="C163" t="n">
-        <v>1.72025652726356</v>
+        <v>1.73500120579647</v>
       </c>
       <c r="D163" t="s">
         <v>13</v>
@@ -2740,7 +2740,7 @@
         <v>12</v>
       </c>
       <c r="C164" t="n">
-        <v>12.0145877843902</v>
+        <v>12.0144376473166</v>
       </c>
       <c r="D164" t="s">
         <v>13</v>
@@ -2754,7 +2754,7 @@
         <v>14</v>
       </c>
       <c r="C165" t="n">
-        <v>5.5617425056576</v>
+        <v>5.53473959702318</v>
       </c>
       <c r="D165" t="s">
         <v>13</v>
@@ -2768,7 +2768,7 @@
         <v>15</v>
       </c>
       <c r="C166" t="n">
-        <v>7.00479164235068</v>
+        <v>7.0040124839821</v>
       </c>
       <c r="D166" t="s">
         <v>13</v>
@@ -2782,7 +2782,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="n">
-        <v>3.68327344527846</v>
+        <v>3.71015822683307</v>
       </c>
       <c r="D167" t="s">
         <v>13</v>
@@ -2796,7 +2796,7 @@
         <v>17</v>
       </c>
       <c r="C168" t="n">
-        <v>4.68792714309571</v>
+        <v>4.70044598750114</v>
       </c>
       <c r="D168" t="s">
         <v>13</v>
@@ -2810,7 +2810,7 @@
         <v>18</v>
       </c>
       <c r="C169" t="n">
-        <v>3.39010192815504</v>
+        <v>3.30761163583207</v>
       </c>
       <c r="D169" t="s">
         <v>13</v>
@@ -2824,7 +2824,7 @@
         <v>19</v>
       </c>
       <c r="C170" t="n">
-        <v>5.53541353862317</v>
+        <v>5.52849323460165</v>
       </c>
       <c r="D170" t="s">
         <v>13</v>
@@ -2852,7 +2852,7 @@
         <v>21</v>
       </c>
       <c r="C172" t="n">
-        <v>1.73750751406281</v>
+        <v>1.7509090708216</v>
       </c>
       <c r="D172" t="s">
         <v>13</v>
@@ -2866,7 +2866,7 @@
         <v>12</v>
       </c>
       <c r="C173" t="n">
-        <v>11.8202780522093</v>
+        <v>11.8203988081985</v>
       </c>
       <c r="D173" t="s">
         <v>13</v>
@@ -2880,7 +2880,7 @@
         <v>14</v>
       </c>
       <c r="C174" t="n">
-        <v>5.55081077369117</v>
+        <v>5.52022195078782</v>
       </c>
       <c r="D174" t="s">
         <v>13</v>
@@ -2894,7 +2894,7 @@
         <v>15</v>
       </c>
       <c r="C175" t="n">
-        <v>6.85994512016889</v>
+        <v>6.85920521071284</v>
       </c>
       <c r="D175" t="s">
         <v>13</v>
@@ -2908,7 +2908,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>3.58782734325691</v>
+        <v>3.61680248730282</v>
       </c>
       <c r="D176" t="s">
         <v>13</v>
@@ -2922,7 +2922,7 @@
         <v>17</v>
       </c>
       <c r="C177" t="n">
-        <v>4.62516703405999</v>
+        <v>4.63751953397768</v>
       </c>
       <c r="D177" t="s">
         <v>13</v>
@@ -2936,7 +2936,7 @@
         <v>18</v>
       </c>
       <c r="C178" t="n">
-        <v>3.37697308992524</v>
+        <v>3.31615423121917</v>
       </c>
       <c r="D178" t="s">
         <v>13</v>
@@ -2950,7 +2950,7 @@
         <v>19</v>
       </c>
       <c r="C179" t="n">
-        <v>5.59774065759576</v>
+        <v>5.58955711756972</v>
       </c>
       <c r="D179" t="s">
         <v>13</v>
@@ -2978,7 +2978,7 @@
         <v>21</v>
       </c>
       <c r="C181" t="n">
-        <v>1.75076791877403</v>
+        <v>1.76815292944953</v>
       </c>
       <c r="D181" t="s">
         <v>13</v>
@@ -2992,7 +2992,7 @@
         <v>12</v>
       </c>
       <c r="C182" t="n">
-        <v>12.6174207753453</v>
+        <v>12.6242478461416</v>
       </c>
       <c r="D182" t="s">
         <v>13</v>
@@ -3006,7 +3006,7 @@
         <v>14</v>
       </c>
       <c r="C183" t="n">
-        <v>6.11220786647131</v>
+        <v>6.03140147625912</v>
       </c>
       <c r="D183" t="s">
         <v>13</v>
@@ -3020,7 +3020,7 @@
         <v>15</v>
       </c>
       <c r="C184" t="n">
-        <v>7.15208793141825</v>
+        <v>7.15278223486535</v>
       </c>
       <c r="D184" t="s">
         <v>13</v>
@@ -3034,7 +3034,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>3.65921365583397</v>
+        <v>3.68805156368964</v>
       </c>
       <c r="D185" t="s">
         <v>13</v>
@@ -3048,7 +3048,7 @@
         <v>17</v>
       </c>
       <c r="C186" t="n">
-        <v>4.84512390091881</v>
+        <v>4.86595911541234</v>
       </c>
       <c r="D186" t="s">
         <v>13</v>
@@ -3062,7 +3062,7 @@
         <v>18</v>
       </c>
       <c r="C187" t="n">
-        <v>3.60051598957052</v>
+        <v>3.54461398272543</v>
       </c>
       <c r="D187" t="s">
         <v>13</v>
@@ -3076,7 +3076,7 @@
         <v>19</v>
       </c>
       <c r="C188" t="n">
-        <v>5.62387141443406</v>
+        <v>5.61481136765997</v>
       </c>
       <c r="D188" t="s">
         <v>13</v>
@@ -3104,7 +3104,7 @@
         <v>21</v>
       </c>
       <c r="C190" t="n">
-        <v>1.80829087343712</v>
+        <v>1.82791596098818</v>
       </c>
       <c r="D190" t="s">
         <v>13</v>
@@ -3118,7 +3118,7 @@
         <v>12</v>
       </c>
       <c r="C191" t="n">
-        <v>13.2366711527301</v>
+        <v>13.2462069724268</v>
       </c>
       <c r="D191" t="s">
         <v>13</v>
@@ -3132,7 +3132,7 @@
         <v>14</v>
       </c>
       <c r="C192" t="n">
-        <v>6.34180626570988</v>
+        <v>6.25606588049339</v>
       </c>
       <c r="D192" t="s">
         <v>13</v>
@@ -3146,7 +3146,7 @@
         <v>15</v>
       </c>
       <c r="C193" t="n">
-        <v>7.26936951112476</v>
+        <v>7.27340584082715</v>
       </c>
       <c r="D193" t="s">
         <v>13</v>
@@ -3160,7 +3160,7 @@
         <v>16</v>
       </c>
       <c r="C194" t="n">
-        <v>3.60747356754444</v>
+        <v>3.62721366990057</v>
       </c>
       <c r="D194" t="s">
         <v>13</v>
@@ -3174,7 +3174,7 @@
         <v>17</v>
       </c>
       <c r="C195" t="n">
-        <v>4.98985705877763</v>
+        <v>5.01737423918502</v>
       </c>
       <c r="D195" t="s">
         <v>13</v>
@@ -3188,7 +3188,7 @@
         <v>18</v>
       </c>
       <c r="C196" t="n">
-        <v>3.80911772310901</v>
+        <v>3.73471540516865</v>
       </c>
       <c r="D196" t="s">
         <v>13</v>
@@ -3202,7 +3202,7 @@
         <v>19</v>
       </c>
       <c r="C197" t="n">
-        <v>5.69308949138981</v>
+        <v>5.68412097774776</v>
       </c>
       <c r="D197" t="s">
         <v>13</v>
@@ -3230,7 +3230,7 @@
         <v>21</v>
       </c>
       <c r="C199" t="n">
-        <v>1.84503399450269</v>
+        <v>1.86870216582304</v>
       </c>
       <c r="D199" t="s">
         <v>13</v>
@@ -3244,7 +3244,7 @@
         <v>12</v>
       </c>
       <c r="C200" t="n">
-        <v>13.5205116761484</v>
+        <v>13.5314486662739</v>
       </c>
       <c r="D200" t="s">
         <v>13</v>
@@ -3258,7 +3258,7 @@
         <v>14</v>
       </c>
       <c r="C201" t="n">
-        <v>6.36487831189715</v>
+        <v>6.29669321014297</v>
       </c>
       <c r="D201" t="s">
         <v>13</v>
@@ -3272,7 +3272,7 @@
         <v>15</v>
       </c>
       <c r="C202" t="n">
-        <v>7.32854562272566</v>
+        <v>7.32076300065079</v>
       </c>
       <c r="D202" t="s">
         <v>13</v>
@@ -3286,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>3.56109853692898</v>
+        <v>3.58346667856431</v>
       </c>
       <c r="D203" t="s">
         <v>13</v>
@@ -3300,7 +3300,7 @@
         <v>17</v>
       </c>
       <c r="C204" t="n">
-        <v>5.07316722886048</v>
+        <v>5.10378889020694</v>
       </c>
       <c r="D204" t="s">
         <v>13</v>
@@ -3314,7 +3314,7 @@
         <v>18</v>
       </c>
       <c r="C205" t="n">
-        <v>3.95629048925701</v>
+        <v>3.86228653398766</v>
       </c>
       <c r="D205" t="s">
         <v>13</v>
@@ -3328,7 +3328,7 @@
         <v>19</v>
       </c>
       <c r="C206" t="n">
-        <v>5.73800359814399</v>
+        <v>5.72697210202412</v>
       </c>
       <c r="D206" t="s">
         <v>13</v>
@@ -3356,7 +3356,7 @@
         <v>21</v>
       </c>
       <c r="C208" t="n">
-        <v>1.87852635790573</v>
+        <v>1.90101565887357</v>
       </c>
       <c r="D208" t="s">
         <v>13</v>
@@ -3370,7 +3370,7 @@
         <v>12</v>
       </c>
       <c r="C209" t="n">
-        <v>13.7779078259325</v>
+        <v>13.7924739807055</v>
       </c>
       <c r="D209" t="s">
         <v>13</v>
@@ -3384,7 +3384,7 @@
         <v>14</v>
       </c>
       <c r="C210" t="n">
-        <v>6.36730863663</v>
+        <v>6.33386126912674</v>
       </c>
       <c r="D210" t="s">
         <v>13</v>
@@ -3398,7 +3398,7 @@
         <v>15</v>
       </c>
       <c r="C211" t="n">
-        <v>7.51205856752223</v>
+        <v>7.50537576583557</v>
       </c>
       <c r="D211" t="s">
         <v>13</v>
@@ -3412,7 +3412,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>3.68534797098544</v>
+        <v>3.70849393056737</v>
       </c>
       <c r="D212" t="s">
         <v>13</v>
@@ -3426,7 +3426,7 @@
         <v>17</v>
       </c>
       <c r="C213" t="n">
-        <v>5.06932650739795</v>
+        <v>5.11777526976762</v>
       </c>
       <c r="D213" t="s">
         <v>13</v>
@@ -3440,7 +3440,7 @@
         <v>18</v>
       </c>
       <c r="C214" t="n">
-        <v>4.09422077826282</v>
+        <v>4.00964317456453</v>
       </c>
       <c r="D214" t="s">
         <v>13</v>
@@ -3454,7 +3454,7 @@
         <v>19</v>
       </c>
       <c r="C215" t="n">
-        <v>5.8011048911505</v>
+        <v>5.78924707918878</v>
       </c>
       <c r="D215" t="s">
         <v>13</v>
@@ -3482,7 +3482,7 @@
         <v>21</v>
       </c>
       <c r="C217" t="n">
-        <v>1.88810347103687</v>
+        <v>1.92418244151693</v>
       </c>
       <c r="D217" t="s">
         <v>13</v>
@@ -3496,7 +3496,7 @@
         <v>12</v>
       </c>
       <c r="C218" t="n">
-        <v>13.8423837127589</v>
+        <v>13.8427423744776</v>
       </c>
       <c r="D218" t="s">
         <v>13</v>
@@ -3510,7 +3510,7 @@
         <v>14</v>
       </c>
       <c r="C219" t="n">
-        <v>6.43564415410248</v>
+        <v>6.39374964623191</v>
       </c>
       <c r="D219" t="s">
         <v>13</v>
@@ -3524,7 +3524,7 @@
         <v>15</v>
       </c>
       <c r="C220" t="n">
-        <v>7.63523198490078</v>
+        <v>7.62852742701633</v>
       </c>
       <c r="D220" t="s">
         <v>13</v>
@@ -3538,7 +3538,7 @@
         <v>16</v>
       </c>
       <c r="C221" t="n">
-        <v>3.62569357180194</v>
+        <v>3.65023935672164</v>
       </c>
       <c r="D221" t="s">
         <v>13</v>
@@ -3552,7 +3552,7 @@
         <v>17</v>
       </c>
       <c r="C222" t="n">
-        <v>5.03168334340876</v>
+        <v>5.07940040641969</v>
       </c>
       <c r="D222" t="s">
         <v>13</v>
@@ -3566,7 +3566,7 @@
         <v>18</v>
       </c>
       <c r="C223" t="n">
-        <v>4.26103685041738</v>
+        <v>4.16668253626413</v>
       </c>
       <c r="D223" t="s">
         <v>13</v>
@@ -3580,7 +3580,7 @@
         <v>19</v>
       </c>
       <c r="C224" t="n">
-        <v>5.81394332661085</v>
+        <v>5.80903942738298</v>
       </c>
       <c r="D224" t="s">
         <v>13</v>
@@ -3608,7 +3608,7 @@
         <v>21</v>
       </c>
       <c r="C226" t="n">
-        <v>1.91517247175151</v>
+        <v>1.9650101614229</v>
       </c>
       <c r="D226" t="s">
         <v>13</v>
@@ -3622,7 +3622,7 @@
         <v>12</v>
       </c>
       <c r="C227" t="n">
-        <v>13.5442448215369</v>
+        <v>13.5486463709071</v>
       </c>
       <c r="D227" t="s">
         <v>13</v>
@@ -3636,7 +3636,7 @@
         <v>14</v>
       </c>
       <c r="C228" t="n">
-        <v>6.31900569916033</v>
+        <v>6.27128509126122</v>
       </c>
       <c r="D228" t="s">
         <v>13</v>
@@ -3650,7 +3650,7 @@
         <v>15</v>
       </c>
       <c r="C229" t="n">
-        <v>7.86902207428667</v>
+        <v>7.8655720432599</v>
       </c>
       <c r="D229" t="s">
         <v>13</v>
@@ -3664,7 +3664,7 @@
         <v>16</v>
       </c>
       <c r="C230" t="n">
-        <v>3.65023826094895</v>
+        <v>3.67391317731283</v>
       </c>
       <c r="D230" t="s">
         <v>13</v>
@@ -3678,7 +3678,7 @@
         <v>17</v>
       </c>
       <c r="C231" t="n">
-        <v>5.08907567705125</v>
+        <v>5.13812663053885</v>
       </c>
       <c r="D231" t="s">
         <v>13</v>
@@ -3692,7 +3692,7 @@
         <v>18</v>
       </c>
       <c r="C232" t="n">
-        <v>4.17766730888707</v>
+        <v>4.18419082243306</v>
       </c>
       <c r="D232" t="s">
         <v>13</v>
@@ -3706,7 +3706,7 @@
         <v>19</v>
       </c>
       <c r="C233" t="n">
-        <v>5.86019539274328</v>
+        <v>5.85322652975115</v>
       </c>
       <c r="D233" t="s">
         <v>13</v>
@@ -3734,7 +3734,7 @@
         <v>21</v>
       </c>
       <c r="C235" t="n">
-        <v>1.94938824244882</v>
+        <v>2.01846763387656</v>
       </c>
       <c r="D235" t="s">
         <v>13</v>
@@ -3748,7 +3748,7 @@
         <v>12</v>
       </c>
       <c r="C236" t="n">
-        <v>13.6008783238747</v>
+        <v>13.614625309462</v>
       </c>
       <c r="D236" t="s">
         <v>13</v>
@@ -3762,7 +3762,7 @@
         <v>14</v>
       </c>
       <c r="C237" t="n">
-        <v>6.16124761793303</v>
+        <v>6.12150689627507</v>
       </c>
       <c r="D237" t="s">
         <v>13</v>
@@ -3776,7 +3776,7 @@
         <v>15</v>
       </c>
       <c r="C238" t="n">
-        <v>8.02183308510245</v>
+        <v>8.0283132509976</v>
       </c>
       <c r="D238" t="s">
         <v>13</v>
@@ -3790,7 +3790,7 @@
         <v>16</v>
       </c>
       <c r="C239" t="n">
-        <v>3.67688352484973</v>
+        <v>3.70210162776015</v>
       </c>
       <c r="D239" t="s">
         <v>13</v>
@@ -3804,7 +3804,7 @@
         <v>17</v>
       </c>
       <c r="C240" t="n">
-        <v>4.98216984486715</v>
+        <v>5.05962256173749</v>
       </c>
       <c r="D240" t="s">
         <v>13</v>
@@ -3818,7 +3818,7 @@
         <v>18</v>
       </c>
       <c r="C241" t="n">
-        <v>4.34190769194702</v>
+        <v>4.36575634655674</v>
       </c>
       <c r="D241" t="s">
         <v>13</v>
@@ -3832,7 +3832,7 @@
         <v>19</v>
       </c>
       <c r="C242" t="n">
-        <v>5.91983254731416</v>
+        <v>5.91322279425897</v>
       </c>
       <c r="D242" t="s">
         <v>13</v>
@@ -3860,7 +3860,7 @@
         <v>21</v>
       </c>
       <c r="C244" t="n">
-        <v>1.96879748783547</v>
+        <v>2.05622033978231</v>
       </c>
       <c r="D244" t="s">
         <v>13</v>
@@ -3874,7 +3874,7 @@
         <v>12</v>
       </c>
       <c r="C245" t="n">
-        <v>13.9254536795804</v>
+        <v>13.9500677022804</v>
       </c>
       <c r="D245" t="s">
         <v>13</v>
@@ -3888,7 +3888,7 @@
         <v>14</v>
       </c>
       <c r="C246" t="n">
-        <v>6.08220001568355</v>
+        <v>6.04774933292145</v>
       </c>
       <c r="D246" t="s">
         <v>13</v>
@@ -3902,7 +3902,7 @@
         <v>15</v>
       </c>
       <c r="C247" t="n">
-        <v>8.21617214869118</v>
+        <v>8.22170303654012</v>
       </c>
       <c r="D247" t="s">
         <v>13</v>
@@ -3916,7 +3916,7 @@
         <v>16</v>
       </c>
       <c r="C248" t="n">
-        <v>3.7491378055354</v>
+        <v>3.77550338217164</v>
       </c>
       <c r="D248" t="s">
         <v>13</v>
@@ -3930,7 +3930,7 @@
         <v>17</v>
       </c>
       <c r="C249" t="n">
-        <v>5.11943874169634</v>
+        <v>5.19305613761938</v>
       </c>
       <c r="D249" t="s">
         <v>13</v>
@@ -3944,7 +3944,7 @@
         <v>18</v>
       </c>
       <c r="C250" t="n">
-        <v>4.47040779859263</v>
+        <v>4.5087674773807</v>
       </c>
       <c r="D250" t="s">
         <v>13</v>
@@ -3958,7 +3958,7 @@
         <v>19</v>
       </c>
       <c r="C251" t="n">
-        <v>5.93659232958971</v>
+        <v>5.92884174585365</v>
       </c>
       <c r="D251" t="s">
         <v>13</v>
@@ -3986,7 +3986,7 @@
         <v>21</v>
       </c>
       <c r="C253" t="n">
-        <v>2.00162266606296</v>
+        <v>2.10953729733164</v>
       </c>
       <c r="D253" t="s">
         <v>13</v>
@@ -4000,7 +4000,7 @@
         <v>12</v>
       </c>
       <c r="C254" t="n">
-        <v>14.3606895743061</v>
+        <v>14.3736200697988</v>
       </c>
       <c r="D254" t="s">
         <v>13</v>
@@ -4014,7 +4014,7 @@
         <v>14</v>
       </c>
       <c r="C255" t="n">
-        <v>6.20909937615775</v>
+        <v>6.1241501393272</v>
       </c>
       <c r="D255" t="s">
         <v>13</v>
@@ -4028,7 +4028,7 @@
         <v>15</v>
       </c>
       <c r="C256" t="n">
-        <v>8.4087140005008</v>
+        <v>8.42508054261301</v>
       </c>
       <c r="D256" t="s">
         <v>13</v>
@@ -4042,7 +4042,7 @@
         <v>16</v>
       </c>
       <c r="C257" t="n">
-        <v>3.76507222916858</v>
+        <v>3.78947259677142</v>
       </c>
       <c r="D257" t="s">
         <v>13</v>
@@ -4056,7 +4056,7 @@
         <v>17</v>
       </c>
       <c r="C258" t="n">
-        <v>5.26929261385416</v>
+        <v>5.35729270965675</v>
       </c>
       <c r="D258" t="s">
         <v>13</v>
@@ -4070,7 +4070,7 @@
         <v>18</v>
       </c>
       <c r="C259" t="n">
-        <v>4.60647210357247</v>
+        <v>4.67527402561165</v>
       </c>
       <c r="D259" t="s">
         <v>13</v>
@@ -4084,7 +4084,7 @@
         <v>19</v>
       </c>
       <c r="C260" t="n">
-        <v>5.94657748743636</v>
+        <v>5.94997141005188</v>
       </c>
       <c r="D260" t="s">
         <v>13</v>
@@ -4112,7 +4112,7 @@
         <v>21</v>
       </c>
       <c r="C262" t="n">
-        <v>2.02536576822241</v>
+        <v>2.14911766122293</v>
       </c>
       <c r="D262" t="s">
         <v>13</v>
@@ -4126,7 +4126,7 @@
         <v>12</v>
       </c>
       <c r="C263" t="n">
-        <v>14.2501072525145</v>
+        <v>14.2647263487798</v>
       </c>
       <c r="D263" t="s">
         <v>13</v>
@@ -4140,7 +4140,7 @@
         <v>14</v>
       </c>
       <c r="C264" t="n">
-        <v>6.25002622712112</v>
+        <v>6.12886742759961</v>
       </c>
       <c r="D264" t="s">
         <v>13</v>
@@ -4154,7 +4154,7 @@
         <v>15</v>
       </c>
       <c r="C265" t="n">
-        <v>8.42816129971524</v>
+        <v>8.50602876786664</v>
       </c>
       <c r="D265" t="s">
         <v>13</v>
@@ -4168,7 +4168,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>3.69600512452588</v>
+        <v>3.72208675593937</v>
       </c>
       <c r="D266" t="s">
         <v>13</v>
@@ -4182,7 +4182,7 @@
         <v>17</v>
       </c>
       <c r="C267" t="n">
-        <v>5.44326634947852</v>
+        <v>5.52992915559069</v>
       </c>
       <c r="D267" t="s">
         <v>13</v>
@@ -4196,7 +4196,7 @@
         <v>18</v>
       </c>
       <c r="C268" t="n">
-        <v>4.75923296260772</v>
+        <v>4.85928231471878</v>
       </c>
       <c r="D268" t="s">
         <v>13</v>
@@ -4210,7 +4210,7 @@
         <v>19</v>
       </c>
       <c r="C269" t="n">
-        <v>5.9890447599707</v>
+        <v>5.98961248800745</v>
       </c>
       <c r="D269" t="s">
         <v>13</v>
@@ -4238,7 +4238,7 @@
         <v>21</v>
       </c>
       <c r="C271" t="n">
-        <v>2.04327488412576</v>
+        <v>2.17594630722841</v>
       </c>
       <c r="D271" t="s">
         <v>13</v>
@@ -4252,7 +4252,7 @@
         <v>12</v>
       </c>
       <c r="C272" t="n">
-        <v>13.833447273637</v>
+        <v>13.8874479048153</v>
       </c>
       <c r="D272" t="s">
         <v>13</v>
@@ -4266,7 +4266,7 @@
         <v>14</v>
       </c>
       <c r="C273" t="n">
-        <v>6.20470208804088</v>
+        <v>6.03109975530493</v>
       </c>
       <c r="D273" t="s">
         <v>13</v>
@@ -4280,7 +4280,7 @@
         <v>15</v>
       </c>
       <c r="C274" t="n">
-        <v>7.22402081783534</v>
+        <v>7.37615839233349</v>
       </c>
       <c r="D274" t="s">
         <v>13</v>
@@ -4294,7 +4294,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>3.63082776354346</v>
+        <v>3.65490102181995</v>
       </c>
       <c r="D275" t="s">
         <v>13</v>
@@ -4308,7 +4308,7 @@
         <v>17</v>
       </c>
       <c r="C276" t="n">
-        <v>5.13854331126972</v>
+        <v>5.19693836114989</v>
       </c>
       <c r="D276" t="s">
         <v>13</v>
@@ -4322,7 +4322,7 @@
         <v>18</v>
       </c>
       <c r="C277" t="n">
-        <v>4.85208927276325</v>
+        <v>4.96598669753572</v>
       </c>
       <c r="D277" t="s">
         <v>13</v>
@@ -4336,7 +4336,7 @@
         <v>19</v>
       </c>
       <c r="C278" t="n">
-        <v>6.0884076688966</v>
+        <v>6.10154493242689</v>
       </c>
       <c r="D278" t="s">
         <v>13</v>
@@ -4364,7 +4364,7 @@
         <v>21</v>
       </c>
       <c r="C280" t="n">
-        <v>2.04125243568366</v>
+        <v>2.14229614379055</v>
       </c>
       <c r="D280" t="s">
         <v>13</v>
@@ -4378,7 +4378,7 @@
         <v>12</v>
       </c>
       <c r="C281" t="n">
-        <v>14.9279607125153</v>
+        <v>14.9846493216371</v>
       </c>
       <c r="D281" t="s">
         <v>13</v>
@@ -4392,7 +4392,7 @@
         <v>14</v>
       </c>
       <c r="C282" t="n">
-        <v>6.35108318665887</v>
+        <v>6.1652603152512</v>
       </c>
       <c r="D282" t="s">
         <v>13</v>
@@ -4406,7 +4406,7 @@
         <v>15</v>
       </c>
       <c r="C283" t="n">
-        <v>7.78814035438882</v>
+        <v>7.95470318726381</v>
       </c>
       <c r="D283" t="s">
         <v>13</v>
@@ -4420,7 +4420,7 @@
         <v>16</v>
       </c>
       <c r="C284" t="n">
-        <v>3.67474397502566</v>
+        <v>3.69316408282158</v>
       </c>
       <c r="D284" t="s">
         <v>13</v>
@@ -4434,7 +4434,7 @@
         <v>17</v>
       </c>
       <c r="C285" t="n">
-        <v>5.30157628272005</v>
+        <v>5.40205774165341</v>
       </c>
       <c r="D285" t="s">
         <v>13</v>
@@ -4448,7 +4448,7 @@
         <v>18</v>
       </c>
       <c r="C286" t="n">
-        <v>5.03108086336033</v>
+        <v>5.19000736681519</v>
       </c>
       <c r="D286" t="s">
         <v>13</v>
@@ -4462,7 +4462,7 @@
         <v>19</v>
       </c>
       <c r="C287" t="n">
-        <v>6.11533446954866</v>
+        <v>6.13589162095234</v>
       </c>
       <c r="D287" t="s">
         <v>13</v>
@@ -4490,7 +4490,7 @@
         <v>21</v>
       </c>
       <c r="C289" t="n">
-        <v>2.05369681897703</v>
+        <v>2.15393643781952</v>
       </c>
       <c r="D289" t="s">
         <v>13</v>
@@ -4504,7 +4504,7 @@
         <v>12</v>
       </c>
       <c r="C290" t="n">
-        <v>15.1088906666712</v>
+        <v>15.1669113309851</v>
       </c>
       <c r="D290" t="s">
         <v>13</v>
@@ -4518,7 +4518,7 @@
         <v>14</v>
       </c>
       <c r="C291" t="n">
-        <v>6.30613952304535</v>
+        <v>6.15046617792669</v>
       </c>
       <c r="D291" t="s">
         <v>13</v>
@@ -4532,7 +4532,7 @@
         <v>15</v>
       </c>
       <c r="C292" t="n">
-        <v>8.10389716348417</v>
+        <v>8.2693621198086</v>
       </c>
       <c r="D292" t="s">
         <v>13</v>
@@ -4546,7 +4546,7 @@
         <v>16</v>
       </c>
       <c r="C293" t="n">
-        <v>3.6103826263547</v>
+        <v>3.62467110479431</v>
       </c>
       <c r="D293" t="s">
         <v>13</v>
@@ -4560,7 +4560,7 @@
         <v>17</v>
       </c>
       <c r="C294" t="n">
-        <v>5.48126259903709</v>
+        <v>5.52392883534119</v>
       </c>
       <c r="D294" t="s">
         <v>13</v>
@@ -4574,7 +4574,7 @@
         <v>18</v>
       </c>
       <c r="C295" t="n">
-        <v>4.99578571921546</v>
+        <v>5.23524330495024</v>
       </c>
       <c r="D295" t="s">
         <v>13</v>
@@ -4588,7 +4588,7 @@
         <v>19</v>
       </c>
       <c r="C296" t="n">
-        <v>6.15778620450516</v>
+        <v>6.17682993966183</v>
       </c>
       <c r="D296" t="s">
         <v>13</v>
@@ -4616,7 +4616,7 @@
         <v>21</v>
       </c>
       <c r="C298" t="n">
-        <v>2.03959677579175</v>
+        <v>2.14350001192504</v>
       </c>
       <c r="D298" t="s">
         <v>13</v>
@@ -4630,7 +4630,7 @@
         <v>12</v>
       </c>
       <c r="C299" t="n">
-        <v>15.4086878587123</v>
+        <v>15.498417360097</v>
       </c>
       <c r="D299" t="s">
         <v>13</v>
@@ -4644,7 +4644,7 @@
         <v>14</v>
       </c>
       <c r="C300" t="n">
-        <v>6.37186386010685</v>
+        <v>6.1996350557604</v>
       </c>
       <c r="D300" t="s">
         <v>13</v>
@@ -4658,7 +4658,7 @@
         <v>15</v>
       </c>
       <c r="C301" t="n">
-        <v>8.34543026735021</v>
+        <v>8.44667455433676</v>
       </c>
       <c r="D301" t="s">
         <v>13</v>
@@ -4672,7 +4672,7 @@
         <v>16</v>
       </c>
       <c r="C302" t="n">
-        <v>3.52704961011059</v>
+        <v>3.53389153035428</v>
       </c>
       <c r="D302" t="s">
         <v>13</v>
@@ -4686,7 +4686,7 @@
         <v>17</v>
       </c>
       <c r="C303" t="n">
-        <v>5.62335253787739</v>
+        <v>5.67517810023031</v>
       </c>
       <c r="D303" t="s">
         <v>13</v>
@@ -4700,7 +4700,7 @@
         <v>18</v>
       </c>
       <c r="C304" t="n">
-        <v>5.06098917471218</v>
+        <v>5.30541618238423</v>
       </c>
       <c r="D304" t="s">
         <v>13</v>
@@ -4714,7 +4714,7 @@
         <v>19</v>
       </c>
       <c r="C305" t="n">
-        <v>6.22830904091248</v>
+        <v>6.27094102894649</v>
       </c>
       <c r="D305" t="s">
         <v>13</v>
@@ -4742,7 +4742,7 @@
         <v>21</v>
       </c>
       <c r="C307" t="n">
-        <v>2.0337095666835</v>
+        <v>2.15314659012364</v>
       </c>
       <c r="D307" t="s">
         <v>13</v>
@@ -4756,7 +4756,7 @@
         <v>12</v>
       </c>
       <c r="C308" t="n">
-        <v>15.6439737548625</v>
+        <v>15.8667534841396</v>
       </c>
       <c r="D308" t="s">
         <v>13</v>
@@ -4770,7 +4770,7 @@
         <v>14</v>
       </c>
       <c r="C309" t="n">
-        <v>6.50308906139091</v>
+        <v>6.20767146871879</v>
       </c>
       <c r="D309" t="s">
         <v>13</v>
@@ -4784,7 +4784,7 @@
         <v>15</v>
       </c>
       <c r="C310" t="n">
-        <v>8.44485589550872</v>
+        <v>8.64559508691523</v>
       </c>
       <c r="D310" t="s">
         <v>13</v>
@@ -4798,7 +4798,7 @@
         <v>16</v>
       </c>
       <c r="C311" t="n">
-        <v>3.57828715126705</v>
+        <v>3.52929325742178</v>
       </c>
       <c r="D311" t="s">
         <v>13</v>
@@ -4812,7 +4812,7 @@
         <v>17</v>
       </c>
       <c r="C312" t="n">
-        <v>5.71226571633973</v>
+        <v>5.7503343624824</v>
       </c>
       <c r="D312" t="s">
         <v>13</v>
@@ -4826,7 +4826,7 @@
         <v>18</v>
       </c>
       <c r="C313" t="n">
-        <v>5.09769276741805</v>
+        <v>5.37330233429269</v>
       </c>
       <c r="D313" t="s">
         <v>13</v>
@@ -4840,7 +4840,7 @@
         <v>19</v>
       </c>
       <c r="C314" t="n">
-        <v>6.25144144546835</v>
+        <v>6.32101519860466</v>
       </c>
       <c r="D314" t="s">
         <v>13</v>
@@ -4868,9 +4868,135 @@
         <v>21</v>
       </c>
       <c r="C316" t="n">
-        <v>2.03979650648914</v>
+        <v>2.17094314948878</v>
       </c>
       <c r="D316" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B317" t="s">
+        <v>12</v>
+      </c>
+      <c r="C317" t="n">
+        <v>15.8156135086707</v>
+      </c>
+      <c r="D317" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B318" t="s">
+        <v>14</v>
+      </c>
+      <c r="C318" t="n">
+        <v>6.25421955376468</v>
+      </c>
+      <c r="D318" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B319" t="s">
+        <v>15</v>
+      </c>
+      <c r="C319" t="n">
+        <v>8.77408074450181</v>
+      </c>
+      <c r="D319" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B320" t="s">
+        <v>16</v>
+      </c>
+      <c r="C320" t="n">
+        <v>3.57185016026046</v>
+      </c>
+      <c r="D320" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B321" t="s">
+        <v>17</v>
+      </c>
+      <c r="C321" t="n">
+        <v>5.82541536152287</v>
+      </c>
+      <c r="D321" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B322" t="s">
+        <v>18</v>
+      </c>
+      <c r="C322" t="n">
+        <v>5.50271815842304</v>
+      </c>
+      <c r="D322" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B323" t="s">
+        <v>19</v>
+      </c>
+      <c r="C323" t="n">
+        <v>6.33607916065988</v>
+      </c>
+      <c r="D323" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B324" t="s">
+        <v>20</v>
+      </c>
+      <c r="C324" t="n">
+        <v>4.0304</v>
+      </c>
+      <c r="D324" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B325" t="s">
+        <v>21</v>
+      </c>
+      <c r="C325" t="n">
+        <v>2.18362422165865</v>
+      </c>
+      <c r="D325" t="s">
         <v>13</v>
       </c>
     </row>
